--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484164_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484164_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.386900000000001</v>
+        <v>8.964600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7626</v>
+        <v>5.6209</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6243</v>
+        <v>3.3437</v>
       </c>
       <c r="G2" t="n">
         <v>4.6463</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5894</v>
+        <v>0.1671</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1926</v>
+        <v>-0.3344</v>
       </c>
       <c r="U2" t="n">
-        <v>0.782</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>3.9528</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.456</v>
+        <v>5.554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6075</v>
+        <v>3.8739</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8485</v>
+        <v>1.6802</v>
       </c>
       <c r="G3" t="n">
         <v>4.6441</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0329</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9238</v>
+        <v>-0.6574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8909</v>
+        <v>0.7226</v>
       </c>
       <c r="V3" t="n">
         <v>-1.139</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3858</v>
+        <v>3.3206</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8643</v>
+        <v>1.5185</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5216</v>
+        <v>1.8021</v>
       </c>
       <c r="G4" t="n">
         <v>3.7712</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6065</v>
+        <v>0.5413</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.1587</v>
       </c>
       <c r="U4" t="n">
-        <v>0.102</v>
+        <v>0.3825</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7503</v>
+        <v>3.0243</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1045</v>
+        <v>0.2403</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6459</v>
+        <v>2.784</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9823</v>
+        <v>3.1571</v>
       </c>
       <c r="H5" t="n">
-        <v>1.28</v>
+        <v>1.1541</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7023</v>
+        <v>2.003</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2809</v>
+        <v>3.0492</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9932</v>
+        <v>1.6034</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2877</v>
+        <v>1.4458</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7014</v>
+        <v>0.1079</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2867</v>
+        <v>-0.4493</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4146</v>
+        <v>0.5572</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>2.7774</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0854</v>
+        <v>-0.9225</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7993</v>
+        <v>-0.7538</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2862</v>
+        <v>-0.1687</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0713</v>
+        <v>-0.0038</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0713</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5156</v>
+        <v>1.9582</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1281</v>
+        <v>-0.5474</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6437</v>
+        <v>2.5056</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1571</v>
+        <v>2.9823</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1541</v>
+        <v>1.28</v>
       </c>
       <c r="I6" t="n">
-        <v>2.003</v>
+        <v>1.7023</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0492</v>
+        <v>2.2809</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6034</v>
+        <v>0.9932</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4458</v>
+        <v>1.2877</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1079</v>
+        <v>0.7014</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4493</v>
+        <v>0.2867</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5572</v>
+        <v>0.4146</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7774</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4312</v>
+        <v>0.2933</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1222</v>
+        <v>0.1474</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.309</v>
+        <v>0.1459</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0038</v>
+        <v>0.0713</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0675</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9776</v>
+        <v>1.1628</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1423</v>
+        <v>0.0521</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1199</v>
+        <v>1.1107</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5429</v>
+        <v>0.9186</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4264</v>
+        <v>0.5391</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1165</v>
+        <v>0.3796</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2334</v>
+        <v>1.3614</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9461</v>
+        <v>1.3964</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7127</v>
+        <v>-0.0351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3095</v>
+        <v>-0.4428</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8292</v>
+        <v>0.4146</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3752</v>
+        <v>-0.3429</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9238</v>
+        <v>-0.3174</v>
       </c>
       <c r="U7" t="n">
-        <v>1.299</v>
+        <v>-0.0256</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9405</v>
+        <v>-0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4724</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.626</v>
+        <v>1.0757</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3163</v>
+        <v>-0.8759</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9423</v>
+        <v>1.9516</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9186</v>
+        <v>1.5429</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5391</v>
+        <v>1.4264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3796</v>
+        <v>0.1165</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3614</v>
+        <v>1.2334</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3964</v>
+        <v>1.9461</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0351</v>
+        <v>-0.7127</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4428</v>
+        <v>0.3095</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4146</v>
+        <v>0.8292</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8797</v>
+        <v>0.4733</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6858</v>
+        <v>-0.6574</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1939</v>
+        <v>1.1307</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6032</v>
+        <v>-0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6032</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4283</v>
+        <v>0.7789</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8908</v>
+        <v>1.1572</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4625</v>
+        <v>-0.3784</v>
       </c>
       <c r="G9" t="n">
         <v>1.1452</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3634</v>
+        <v>-0.0128</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4251</v>
+        <v>-0.1587</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0617</v>
+        <v>0.1459</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7422</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>C. DIOP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1996</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2243</v>
+        <v>-1.4437</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0247</v>
+        <v>0.915</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9594</v>
+        <v>-0.3813</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7861</v>
+        <v>-1.4009</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8268</v>
+        <v>1.0196</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9968</v>
+        <v>-0.0551</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4025</v>
+        <v>-1.3402</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4057</v>
+        <v>1.2852</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0374</v>
+        <v>-0.3263</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3837</v>
+        <v>-0.0607</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4211</v>
+        <v>-0.2656</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7774</v>
+        <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1133</v>
+        <v>-0.3457</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.442</v>
+        <v>-0.3967</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5554</v>
+        <v>0.051</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.139</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. DIOP</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7429</v>
+        <v>-0.6219</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5457</v>
+        <v>-1.366</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8028</v>
+        <v>0.7441</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3813</v>
+        <v>-0.9594</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4009</v>
+        <v>-2.7861</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0196</v>
+        <v>1.8268</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0551</v>
+        <v>-0.9968</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3402</v>
+        <v>-2.4025</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2852</v>
+        <v>1.4057</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3263</v>
+        <v>0.0374</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0607</v>
+        <v>-0.3837</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2656</v>
+        <v>0.4211</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1903</v>
+        <v>2.7774</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.3089</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4988</v>
+        <v>-0.5837</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0612</v>
+        <v>0.2748</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.139</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.3455</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3385</v>
+        <v>-2.8196</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7762</v>
+        <v>-2.5098</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5623</v>
+        <v>-0.3098</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2887</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6649</v>
+        <v>-0.146</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4251</v>
+        <v>-0.1587</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2398</v>
+        <v>0.0127</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1947</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.2455</v>
+        <v>21.8689</v>
       </c>
       <c r="E13" t="n">
-        <v>5.096800000000002</v>
+        <v>5.720099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>16.1489</v>
+        <v>16.1488</v>
       </c>
       <c r="G13" t="n">
         <v>20.1783</v>
@@ -1444,7 +1444,7 @@
         <v>19.4842</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5658</v>
+        <v>7.565800000000001</v>
       </c>
       <c r="L13" t="n">
         <v>11.9185</v>
@@ -1456,10 +1456,10 @@
         <v>-6.8856</v>
       </c>
       <c r="O13" t="n">
-        <v>7.579700000000001</v>
+        <v>7.5797</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9677</v>
+        <v>3.967700000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.8705</v>
@@ -1468,10 +1468,10 @@
         <v>19.8383</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1623</v>
+        <v>-0.5387</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.335400000000001</v>
+        <v>-3.7121</v>
       </c>
       <c r="U13" t="n">
         <v>3.1733</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1137</v>
+        <v>3.7697</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9542</v>
+        <v>1.1971</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1595</v>
+        <v>2.5726</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0482</v>
+        <v>2.1244</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8801</v>
+        <v>4.551</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8319</v>
+        <v>-2.4266</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5533</v>
+        <v>2.423</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1933</v>
+        <v>4.461</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.64</v>
+        <v>-2.038</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5051</v>
+        <v>-0.2986</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3132</v>
+        <v>0.09</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1918</v>
+        <v>-0.3886</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9758</v>
+        <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2043</v>
+        <v>0.9664</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2495</v>
+        <v>0.0114</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9548</v>
+        <v>0.955</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8692</v>
+        <v>1.4724</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1352</v>
+        <v>1.7384</v>
       </c>
       <c r="X14" t="n">
         <v>-0.266</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9654</v>
+        <v>2.778</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5849</v>
+        <v>0.24</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3805</v>
+        <v>2.538</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1244</v>
+        <v>0.0482</v>
       </c>
       <c r="H15" t="n">
-        <v>4.551</v>
+        <v>1.8801</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4266</v>
+        <v>-1.8319</v>
       </c>
       <c r="J15" t="n">
-        <v>2.423</v>
+        <v>1.5533</v>
       </c>
       <c r="K15" t="n">
-        <v>4.461</v>
+        <v>2.1933</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.038</v>
+        <v>-0.64</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2986</v>
+        <v>-1.5051</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09</v>
+        <v>-0.3132</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3886</v>
+        <v>-1.1918</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1822</v>
+        <v>2.9758</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1621</v>
+        <v>0.8686</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6008</v>
+        <v>-0.4647</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7629</v>
+        <v>1.3333</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4724</v>
+        <v>0.8692</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7384</v>
+        <v>1.1352</v>
       </c>
       <c r="X15" t="n">
         <v>-0.266</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3215</v>
+        <v>1.6719</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5839</v>
+        <v>0.4616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7376</v>
+        <v>1.2103</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8844</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2221</v>
+        <v>0.5725</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2414</v>
+        <v>0.1191</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0193</v>
+        <v>0.4534</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5673</v>
+        <v>-0.3938</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6182</v>
+        <v>1.1284</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1855</v>
+        <v>-1.5222</v>
       </c>
       <c r="G17" t="n">
         <v>0.1151</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4727</v>
+        <v>0.6462</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4137</v>
+        <v>0.0964</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8864</v>
+        <v>0.5498</v>
       </c>
       <c r="V17" t="n">
         <v>-2.1469</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.5939</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2175</v>
+        <v>1.3195</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0538</v>
+        <v>-1.9135</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7079</v>
@@ -1858,13 +1858,13 @@
         <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9381</v>
+        <v>-0.6957</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5498</v>
+        <v>-0.4477</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3883</v>
+        <v>-0.248</v>
       </c>
       <c r="V18" t="n">
         <v>1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3511</v>
+        <v>-1.0569</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9401</v>
+        <v>-1.838</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5889</v>
+        <v>0.7811</v>
       </c>
       <c r="G19" t="n">
         <v>0.4244</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0261</v>
+        <v>0.3202</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4251</v>
+        <v>-0.323</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4511</v>
+        <v>0.6433</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2777</v>
+        <v>-2.2318</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0708</v>
+        <v>-2.9687</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7931</v>
+        <v>0.737</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9872</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0488</v>
+        <v>-0.0028</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4251</v>
+        <v>-0.323</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3763</v>
+        <v>0.3202</v>
       </c>
       <c r="V20" t="n">
         <v>1.5437</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7473</v>
+        <v>-2.7575</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1073</v>
+        <v>-1.0053</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.64</v>
+        <v>-1.7522</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6805</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1757</v>
+        <v>-0.0737</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1009</v>
+        <v>-0.0113</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5868</v>
+        <v>-4.0121</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8345</v>
+        <v>-2.7325</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7522</v>
+        <v>-1.2795</v>
       </c>
       <c r="G22" t="n">
         <v>-5.4344</v>
@@ -2170,13 +2170,13 @@
         <v>2.3806</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4897</v>
+        <v>0.0851</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.544</v>
+        <v>-0.442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0544</v>
+        <v>0.5271</v>
       </c>
       <c r="V22" t="n">
         <v>0.9405</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9308</v>
+        <v>-4.5304</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.657</v>
+        <v>-4.4529</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2738</v>
+        <v>-0.0775</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4496</v>
@@ -2248,13 +2248,13 @@
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4812</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6121</v>
+        <v>-0.408</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1309</v>
+        <v>0.3273</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7942</v>
+        <v>-5.608</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0309</v>
+        <v>-2.9289</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7632</v>
+        <v>-2.6791</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0956</v>
@@ -2326,13 +2326,13 @@
         <v>0.3968</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5163</v>
+        <v>-0.3301</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3627</v>
+        <v>-0.2607</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1536</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6032</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5546</v>
+        <v>-7.6006</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2011</v>
+        <v>-4.3031</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3535</v>
+        <v>-3.2974</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6508</v>
@@ -2404,13 +2404,13 @@
         <v>0.7935</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3763</v>
+        <v>-0.4222</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5554</v>
+        <v>-0.6574</v>
       </c>
       <c r="U25" t="n">
-        <v>0.179</v>
+        <v>0.2352</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3373</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.2454</v>
+        <v>-20.5654</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.883</v>
+        <v>-15.8828</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.362399999999999</v>
+        <v>-4.6824</v>
       </c>
       <c r="G26" t="n">
         <v>-20.1783</v>
@@ -2482,13 +2482,13 @@
         <v>15.8707</v>
       </c>
       <c r="S26" t="n">
-        <v>1.162099999999999</v>
+        <v>1.8425</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.1735</v>
+        <v>-3.1733</v>
       </c>
       <c r="U26" t="n">
-        <v>4.335500000000001</v>
+        <v>5.0158</v>
       </c>
       <c r="V26" t="n">
         <v>1.7384</v>
